--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512441_1ºAA1ºABFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512441_1ºAA1ºABFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5961</v>
+        <v>3.2688</v>
       </c>
       <c r="E2" t="n">
-        <v>2.724</v>
+        <v>2.9901</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8721</v>
+        <v>0.2787</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1464</v>
+        <v>-0.1605</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7977</v>
+        <v>1.814</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.9441</v>
+        <v>-1.9745</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3268</v>
+        <v>2.4946</v>
       </c>
       <c r="K2" t="n">
-        <v>2.841</v>
+        <v>2.9481</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5142</v>
+        <v>-0.4535</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4732</v>
+        <v>-2.6551</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0433</v>
+        <v>-1.1342</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4299</v>
+        <v>-1.521</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0009</v>
+        <v>2.921</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2779</v>
+        <v>-0.5533</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8623</v>
+        <v>-0.8103</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5844</v>
+        <v>0.257</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2196</v>
+        <v>1.2563</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.24</v>
+        <v>-0.2442</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6189</v>
+        <v>2.7612</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1632</v>
+        <v>1.3945</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4558</v>
+        <v>1.3667</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7156</v>
+        <v>3.728</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1422</v>
+        <v>1.1474</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5734</v>
+        <v>2.5806</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5594</v>
+        <v>3.62</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9997</v>
+        <v>1.0263</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5596</v>
+        <v>2.5937</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1562</v>
+        <v>0.108</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1425</v>
+        <v>0.1211</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.497</v>
+        <v>-0.3299</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5157</v>
+        <v>-0.395</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0186</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3107</v>
+        <v>1.4145</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7377</v>
+        <v>2.2542</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4271</v>
+        <v>-0.8396</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3773</v>
+        <v>-0.3205</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8689</v>
+        <v>0.7236</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4916</v>
+        <v>-1.0442</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2452</v>
+        <v>2.1175</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9543</v>
+        <v>1.242</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1995</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6226</v>
+        <v>-2.438</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9146</v>
+        <v>-0.5184</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7079</v>
+        <v>-1.9197</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6005</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2001</v>
+        <v>-1.9474</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S4" t="n">
-        <v>0.148</v>
+        <v>-0.2681</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3466</v>
+        <v>-0.3581</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4946</v>
+        <v>0.09</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0605</v>
+        <v>2.1979</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0392</v>
+        <v>2.4421</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0996</v>
+        <v>-0.2442</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.15</v>
+        <v>0.7349</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7211</v>
+        <v>2.7652</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8711</v>
+        <v>-2.0303</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5471</v>
+        <v>-0.4126</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.951</v>
+        <v>-1.8745</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5961</v>
+        <v>1.4619</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3103</v>
+        <v>2.357</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.8851</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7523</v>
+        <v>3.2421</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2368</v>
+        <v>-2.7696</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.393</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1562</v>
+        <v>-1.7802</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0006</v>
+        <v>1.5579</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0006</v>
+        <v>1.7526</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9564</v>
+        <v>-0.3941</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5891999999999999</v>
+        <v>-0.515</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3672</v>
+        <v>0.1209</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2598</v>
+        <v>-0.0163</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1179</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2598</v>
+        <v>-1.1342</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4206</v>
+        <v>0.6597</v>
       </c>
       <c r="E6" t="n">
-        <v>1.432</v>
+        <v>-1.2154</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0114</v>
+        <v>1.8751</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3515</v>
+        <v>-1.5227</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6434</v>
+        <v>-0.9637</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9949</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9287</v>
+        <v>-1.2136</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0869</v>
+        <v>-0.5413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8418</v>
+        <v>-0.6722</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2802</v>
+        <v>-0.3091</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4435</v>
+        <v>-0.4224</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8367</v>
+        <v>0.1132</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2001</v>
+        <v>1.9474</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8005</v>
+        <v>1.9474</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1874</v>
+        <v>0.5145</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.0018</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2917</v>
+        <v>0.5164</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1596</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3995</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.24</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3812</v>
+        <v>-0.1647</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9166</v>
+        <v>-1.9979</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2978</v>
+        <v>1.8332</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8074</v>
+        <v>0.758</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0825</v>
+        <v>0.0595</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7249</v>
+        <v>0.6985</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1798</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3399</v>
+        <v>0.3489</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8399</v>
+        <v>0.8511</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3724</v>
+        <v>-0.442</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2574</v>
+        <v>-0.2895</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.115</v>
+        <v>-0.1526</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7742</v>
+        <v>0.2457</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0955</v>
+        <v>-0.2769</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8697</v>
+        <v>0.5226</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1934</v>
+        <v>-0.2104</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0766</v>
+        <v>1.8571</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.27</v>
+        <v>-2.0675</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.278</v>
+        <v>0.2269</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4137</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8643</v>
+        <v>0.9715</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8343</v>
+        <v>3.74</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3563</v>
+        <v>0.716</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.478</v>
+        <v>3.024</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4437</v>
+        <v>-3.5131</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0574</v>
+        <v>-1.4605</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3862</v>
+        <v>-2.0526</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6002</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-3.1158</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>1.7526</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9237</v>
+        <v>-0.051</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7114</v>
+        <v>-0.2676</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2122</v>
+        <v>0.2166</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4393</v>
+        <v>0.9768</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1998</v>
+        <v>1.5005</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.639</v>
+        <v>-0.5237000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0913</v>
+        <v>-0.7406</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8125</v>
+        <v>-0.4046</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9038</v>
+        <v>-0.336</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0982</v>
+        <v>-1.2671</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7805</v>
+        <v>-0.3869</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8787</v>
+        <v>-0.8803</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4563</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6052</v>
+        <v>-0.3027</v>
       </c>
       <c r="L9" t="n">
-        <v>2.851</v>
+        <v>-0.4619</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.3581</v>
+        <v>-0.5026</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3858</v>
+        <v>-0.0842</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9723</v>
+        <v>-0.4184</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4004</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2009</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8005</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7489</v>
+        <v>0.4497</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9024</v>
+        <v>0.1126</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1535</v>
+        <v>0.3371</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9598</v>
+        <v>-0.5074</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4596</v>
+        <v>1.2211</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4997</v>
+        <v>-1.7284</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6333</v>
+        <v>-2.4325</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.963</v>
+        <v>-1.6877</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6703</v>
+        <v>-0.7448</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5041</v>
+        <v>-1.5345</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2381</v>
+        <v>0.2129</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7422</v>
+        <v>-1.7474</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3181</v>
+        <v>-0.295</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3599</v>
+        <v>0.3695</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.186</v>
+        <v>-1.2394</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0642</v>
+        <v>-1.0829</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7291</v>
+        <v>-0.5085</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6446</v>
+        <v>-0.419</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0895</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9712</v>
+        <v>-6.6832</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4867</v>
+        <v>-5.0984</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4845</v>
+        <v>-1.5848</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4847</v>
+        <v>-4.482</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2461</v>
+        <v>-0.2905</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.2386</v>
+        <v>-4.1915</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6482</v>
+        <v>-2.5465</v>
       </c>
       <c r="K11" t="n">
-        <v>0.14</v>
+        <v>0.1437</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7882</v>
+        <v>-2.6902</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8365</v>
+        <v>-1.9354</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3861</v>
+        <v>-0.4342</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4505</v>
+        <v>-1.5013</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0067</v>
+        <v>-0.697</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6379</v>
+        <v>-0.4098</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3688</v>
+        <v>-0.2873</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0793</v>
+        <v>-0.1411</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0793</v>
+        <v>-0.1411</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.411700000000002</v>
+        <v>-1.3923</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1414</v>
+        <v>0.8570999999999991</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2703</v>
+        <v>-2.2493</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0679</v>
+        <v>-4.987</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3562999999999998</v>
+        <v>-0.3026999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.7116</v>
+        <v>-4.684399999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>9.5853</v>
+        <v>10.7094</v>
       </c>
       <c r="K12" t="n">
-        <v>4.503999999999999</v>
+        <v>5.065400000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>5.0811</v>
+        <v>5.644100000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.6533</v>
+        <v>-15.6963</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.860399999999999</v>
+        <v>-5.3682</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.7928</v>
+        <v>-10.3286</v>
       </c>
       <c r="P12" t="n">
-        <v>3.001</v>
+        <v>2.921</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.0041</v>
+        <v>-13.6315</v>
       </c>
       <c r="R12" t="n">
-        <v>17.0049</v>
+        <v>16.5524</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6447</v>
+        <v>-1.592</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6001</v>
+        <v>-3.3409</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9552</v>
+        <v>1.748899999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3003</v>
+        <v>2.2656</v>
       </c>
       <c r="W12" t="n">
-        <v>6.8775</v>
+        <v>7.119999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.577</v>
+        <v>-4.8543</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3819</v>
+        <v>6.8709</v>
       </c>
       <c r="E13" t="n">
-        <v>7.5522</v>
+        <v>8.0686</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1703</v>
+        <v>-1.1977</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7217</v>
+        <v>4.7763</v>
       </c>
       <c r="H13" t="n">
-        <v>1.011</v>
+        <v>1.0253</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7107</v>
+        <v>3.7511</v>
       </c>
       <c r="J13" t="n">
-        <v>5.6227</v>
+        <v>5.7684</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2614</v>
+        <v>1.3266</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3613</v>
+        <v>4.4418</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.901</v>
+        <v>-0.992</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2505</v>
+        <v>-0.3013</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4068</v>
+        <v>-0.0665</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.509</v>
+        <v>-0.2861</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1022</v>
+        <v>0.2196</v>
       </c>
       <c r="V13" t="n">
-        <v>2.067</v>
+        <v>2.161</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4387</v>
+        <v>3.56</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3717</v>
+        <v>-1.3991</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4077</v>
+        <v>4.3578</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5125</v>
+        <v>2.4861</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8953</v>
+        <v>1.8717</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8221</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6936</v>
+        <v>0.6742</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1285</v>
+        <v>2.1658</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6891</v>
+        <v>1.8385</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4017</v>
+        <v>0.4439</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2874</v>
+        <v>1.3946</v>
       </c>
       <c r="M14" t="n">
-        <v>1.133</v>
+        <v>1.0015</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2919</v>
+        <v>0.2303</v>
       </c>
       <c r="O14" t="n">
-        <v>0.841</v>
+        <v>0.7712</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3622</v>
+        <v>0.5526</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.1587</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5335</v>
+        <v>0.7113</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3476</v>
+        <v>0.381</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3717</v>
+        <v>-1.3991</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3189</v>
+        <v>3.5267</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7216</v>
+        <v>2.2363</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.2903</v>
       </c>
       <c r="G15" t="n">
-        <v>0.858</v>
+        <v>2.5232</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2668</v>
+        <v>1.463</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1248</v>
+        <v>1.0602</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5886</v>
+        <v>3.0494</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9052</v>
+        <v>1.7037</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6834</v>
+        <v>1.3457</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7306</v>
+        <v>-0.5262</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.172</v>
+        <v>-0.2407</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5586</v>
+        <v>-0.2855</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6005</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6007</v>
+        <v>0.9737</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6007</v>
+        <v>0.5194</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1265</v>
+        <v>0.1606</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7272</v>
+        <v>0.3588</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2598</v>
+        <v>0.4841</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.4841</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0662</v>
+        <v>3.244</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6917</v>
+        <v>2.8013</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3745</v>
+        <v>0.4427</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5133</v>
+        <v>0.8487</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4803</v>
+        <v>-0.255</v>
       </c>
       <c r="I16" t="n">
-        <v>1.033</v>
+        <v>1.1037</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9432</v>
+        <v>3.788</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6595</v>
+        <v>1.0239</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2836</v>
+        <v>2.7642</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4298</v>
+        <v>-2.9393</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1792</v>
+        <v>-1.2789</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2506</v>
+        <v>-1.6604</v>
       </c>
       <c r="P16" t="n">
+        <v>1.5579</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.9737</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.5316</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5579</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.2925</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.8505</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-1.0003</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.0003</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.0446</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.2511</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.2958</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.5083</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.5083</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4523</v>
+        <v>0.4535</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0654</v>
+        <v>-0.9466</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6131</v>
+        <v>1.4001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5134</v>
+        <v>1.0214</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6998</v>
+        <v>1.1269</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8136</v>
+        <v>-0.1055</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2212</v>
+        <v>0.3818</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2215</v>
+        <v>1.0058</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9997</v>
+        <v>-0.624</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7078</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5217000000000001</v>
+        <v>0.1211</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1861</v>
+        <v>0.5185</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0003</v>
+        <v>1.1684</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3109</v>
+        <v>0.3569</v>
       </c>
       <c r="T17" t="n">
-        <v>1.525</v>
+        <v>0.3073</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7859</v>
+        <v>0.0496</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3717</v>
+        <v>-1.1196</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6915</v>
+        <v>-0.4575</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8779</v>
+        <v>0.1608</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4273</v>
+        <v>-1.0162</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3051</v>
+        <v>1.177</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0403</v>
+        <v>-0.9707</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1222</v>
+        <v>0.0282</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0819</v>
+        <v>-0.9989</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3417</v>
+        <v>0.3305</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9797</v>
+        <v>0.7518</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.638</v>
+        <v>-0.4213</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6986</v>
+        <v>-1.3012</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1425</v>
+        <v>-0.7236</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5561</v>
+        <v>-0.5775</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2003</v>
+        <v>1.7526</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7494</v>
+        <v>0.3525</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9115</v>
+        <v>-0.6525</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1621</v>
+        <v>1.005</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1119</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6802</v>
+        <v>0.2795</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4317</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4531</v>
+        <v>-0.0309</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5727</v>
+        <v>1.114</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0258</v>
+        <v>-1.1449</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8743</v>
+        <v>1.5158</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0582</v>
+        <v>0.7184</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9324</v>
+        <v>0.7974</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2636</v>
+        <v>3.3118</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7016</v>
+        <v>1.2855</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.438</v>
+        <v>2.0263</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1378</v>
+        <v>-1.796</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6434</v>
+        <v>-0.5671</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4944</v>
+        <v>-1.2289</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8002</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8005</v>
+        <v>0.9737</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5271</v>
+        <v>0.826</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0958</v>
+        <v>0.4116</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6229</v>
+        <v>0.4144</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.3991</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2598</v>
+        <v>-0.6621</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2598</v>
+        <v>-0.737</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4842</v>
+        <v>-1.6209</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0253</v>
+        <v>-0.1424</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5095</v>
+        <v>-1.4785</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9625</v>
+        <v>0.9421</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8177</v>
+        <v>-1.8345</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7802</v>
+        <v>2.7766</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8635</v>
+        <v>1.9342</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.296</v>
+        <v>-1.2674</v>
       </c>
       <c r="L20" t="n">
-        <v>3.1596</v>
+        <v>3.2016</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.901</v>
+        <v>-0.992</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5671</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3794</v>
+        <v>-0.4249</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2132</v>
+        <v>0.1059</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1623</v>
+        <v>-0.1292</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0508</v>
+        <v>0.2351</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.905</v>
+        <v>-6.6912</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.126</v>
+        <v>-3.8925</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.779</v>
+        <v>-2.7987</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.9199</v>
+        <v>-3.9466</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8685</v>
+        <v>-0.9042</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.0514</v>
+        <v>-3.0424</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.934</v>
+        <v>-1.8914</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06</v>
+        <v>0.0616</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.994</v>
+        <v>-1.953</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9858</v>
+        <v>-2.0552</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9285</v>
+        <v>-0.9658</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0574</v>
+        <v>-1.0895</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.645</v>
+        <v>-0.4135</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4512</v>
+        <v>-0.3332</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1939</v>
+        <v>-0.0803</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5399</v>
+        <v>-1.5521</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.1571</v>
+        <v>-8.213900000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.172499999999999</v>
+        <v>-8.459300000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0154</v>
+        <v>0.2454</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.5692</v>
+        <v>-4.5633</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7559</v>
+        <v>-1.7395</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8133</v>
+        <v>-2.8237</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.9464</v>
+        <v>-2.8147</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0343</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9121</v>
+        <v>-1.8475</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6228</v>
+        <v>-1.7486</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7216</v>
+        <v>-0.7723</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9012</v>
+        <v>-0.9762</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.387</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2247</v>
+        <v>-0.7762</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1623</v>
+        <v>0.2413</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4117</v>
+        <v>2.056799999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2701999999999991</v>
+        <v>2.2493</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1415</v>
+        <v>-0.1926000000000006</v>
       </c>
       <c r="G23" t="n">
-        <v>5.0679</v>
+        <v>4.986899999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3561999999999999</v>
+        <v>0.3028000000000004</v>
       </c>
       <c r="I23" t="n">
-        <v>4.711799999999999</v>
+        <v>4.684299999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>14.6532</v>
+        <v>15.6965</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8603</v>
+        <v>5.3682</v>
       </c>
       <c r="L23" t="n">
-        <v>9.792899999999999</v>
+        <v>10.3284</v>
       </c>
       <c r="M23" t="n">
-        <v>-9.585000000000001</v>
+        <v>-10.7094</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.504200000000001</v>
+        <v>-5.0654</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.0812</v>
+        <v>-5.6439</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.0007</v>
+        <v>-2.9211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-17.005</v>
+        <v>-16.5528</v>
       </c>
       <c r="R23" t="n">
-        <v>14.0039</v>
+        <v>13.6315</v>
       </c>
       <c r="S23" t="n">
-        <v>1.6449</v>
+        <v>2.2564</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9552</v>
+        <v>-1.7489</v>
       </c>
       <c r="U23" t="n">
-        <v>3.6</v>
+        <v>4.0053</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.3004</v>
+        <v>-2.2657</v>
       </c>
       <c r="W23" t="n">
-        <v>4.577100000000001</v>
+        <v>4.854299999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.8774</v>
+        <v>-7.1202</v>
       </c>
     </row>
   </sheetData>
